--- a/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_BOM-DALI_LOAD_DigitalLED(V0.1).xlsx
+++ b/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_BOM-DALI_LOAD_DigitalLED(V0.1).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="111">
   <si>
     <t xml:space="preserve">Comment</t>
   </si>
@@ -311,6 +311,9 @@
     <t xml:space="preserve">C8598</t>
   </si>
   <si>
+    <t xml:space="preserve">C53035203</t>
+  </si>
+  <si>
     <t xml:space="preserve">C1002</t>
   </si>
   <si>
@@ -351,9 +354,6 @@
   </si>
   <si>
     <t xml:space="preserve">C970946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C53035203</t>
   </si>
 </sst>
 </file>
@@ -840,7 +840,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -860,7 +860,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -917,7 +917,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -988,7 +988,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1008,7 +1008,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1028,7 +1028,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1068,7 +1068,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1088,7 +1088,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1108,7 +1108,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1128,7 +1128,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1148,7 +1148,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1168,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1188,7 +1188,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
